--- a/sharedata/excel/Z-装备表(EquipData).xlsx
+++ b/sharedata/excel/Z-装备表(EquipData).xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备表(EquipData)" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="84">
-  <si>
-    <t>具体装备、主属性与子属性池、星级概率、套装归属待配置；名称、图标、品质由物品表维护。</t>
-  </si>
-  <si>
-    <t>新手装备不使用的套装、星级、子属性留空；装备引用均填目标表中文索引，列表用//分隔。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="116">
   <si>
     <t>装备表</t>
   </si>
@@ -174,6 +168,99 @@
     <t>size(sub_attr_name)</t>
   </si>
   <si>
+    <t>临时新手_头盔</t>
+  </si>
+  <si>
+    <t>头盔</t>
+  </si>
+  <si>
+    <t>防御固定</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>临时新手_衣服</t>
+  </si>
+  <si>
+    <t>衣服</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>临时新手_武器</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>攻击固定</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>临时新手_鞋子</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>PVE移动力固定</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>临时守卫_头盔</t>
+  </si>
+  <si>
+    <t>临时守卫套装</t>
+  </si>
+  <si>
+    <t>1星//2星//3星//4星</t>
+  </si>
+  <si>
+    <t>60//25//10//5</t>
+  </si>
+  <si>
+    <t>智力固定</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>攻击固定//防御固定//智力固定//统帅固定</t>
+  </si>
+  <si>
+    <t>2//1//2//0.5</t>
+  </si>
+  <si>
+    <t>100//100//100//100</t>
+  </si>
+  <si>
+    <t>临时守卫_衣服</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>临时守卫_武器</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>临时守卫_鞋子</t>
+  </si>
+  <si>
+    <t>先攻固定</t>
+  </si>
+  <si>
     <t>装备部位表</t>
   </si>
   <si>
@@ -210,31 +297,40 @@
     <t>ref(IconData)</t>
   </si>
   <si>
-    <t>头盔</t>
-  </si>
-  <si>
     <t>$Lang$头盔</t>
   </si>
   <si>
-    <t>待配置</t>
-  </si>
-  <si>
-    <t>衣服</t>
+    <t>装备栏剪影-头盔</t>
+  </si>
+  <si>
+    <t>装备界面筛选-头盔</t>
   </si>
   <si>
     <t>$Lang$衣服</t>
   </si>
   <si>
-    <t>武器</t>
+    <t>装备栏剪影-衣服</t>
+  </si>
+  <si>
+    <t>装备界面筛选-衣服</t>
   </si>
   <si>
     <t>$Lang$武器</t>
   </si>
   <si>
-    <t>鞋子</t>
+    <t>装备栏剪影-武器</t>
+  </si>
+  <si>
+    <t>装备界面筛选-武器</t>
   </si>
   <si>
     <t>$Lang$鞋子</t>
+  </si>
+  <si>
+    <t>装备栏剪影-鞋子</t>
+  </si>
+  <si>
+    <t>装备界面筛选-鞋子</t>
   </si>
   <si>
     <t>装备星级表</t>
@@ -314,6 +410,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -468,13 +571,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -802,153 +898,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -965,14 +1061,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1446,518 +1539,512 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="18.75" customWidth="1"/>
-    <col min="6" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="10" width="21.375" customWidth="1"/>
-    <col min="11" max="11" width="16.125" customWidth="1"/>
-    <col min="12" max="12" width="17.25" customWidth="1"/>
-    <col min="13" max="14" width="20.25" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="6" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="6" customWidth="1"/>
+    <col min="9" max="10" width="21.375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="16.125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="39.625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="6" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A1" s="2" t="str">
-        <v>本次补入4件临时新手装备与4件临时守卫套装，用于导表/生成/穿戴联调；红色加粗为临时配置，不作为正式投放或平衡结论。</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A2" s="2" t="s">
+    <row r="1" ht="16.5" spans="1:14">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:14">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" ht="15" spans="1:14">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="3" t="s">
+    </row>
+    <row r="4" ht="16.5" spans="1:14">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="4" t="s">
+    </row>
+    <row r="5" ht="16.5" spans="1:14">
+      <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="4" t="s">
+    </row>
+    <row r="6" ht="16.5" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="J6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="N6" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:14">
+      <c r="A7" s="5"/>
+      <c r="B7" s="7">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" ht="49.5" customHeight="1" spans="1:14">
-      <c r="A7" s="5"/>
-      <c r="B7" s="7" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C7" s="8" t="str">
-        <v>临时新手_头盔</v>
-      </c>
-      <c r="D7" s="7" t="str">
-        <v>头盔</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="7" t="str">
-        <v>防御固定</v>
-      </c>
-      <c r="I7" s="7" t="str">
-        <v>2</v>
-      </c>
-      <c r="J7" s="7" t="str">
-        <v>100</v>
-      </c>
-      <c r="K7" s="7" t="n">
+      <c r="H7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="7">
         <v>1</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" ht="49.5" customHeight="1">
-      <c r="B8" t="n" s="7">
+    <row r="8" ht="15" spans="1:14">
+      <c r="B8" s="7">
         <v>1002</v>
       </c>
-      <c r="C8" t="str" s="8">
-        <v>临时新手_衣服</v>
-      </c>
-      <c r="D8" t="str" s="7">
-        <v>衣服</v>
+      <c r="C8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" t="str" s="7">
-        <v>防御固定</v>
-      </c>
-      <c r="I8" t="str" s="7">
-        <v>3</v>
-      </c>
-      <c r="J8" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K8" t="n" s="7">
+      <c r="H8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="7">
         <v>1</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="B9" t="n" s="7">
+    <row r="9" ht="15" spans="1:14">
+      <c r="B9" s="7">
         <v>1003</v>
       </c>
-      <c r="C9" t="str" s="8">
-        <v>临时新手_武器</v>
-      </c>
-      <c r="D9" t="str" s="7">
-        <v>武器</v>
+      <c r="C9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" t="str" s="7">
-        <v>攻击固定</v>
-      </c>
-      <c r="I9" t="str" s="7">
-        <v>5</v>
-      </c>
-      <c r="J9" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K9" t="n" s="7">
+      <c r="H9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="7">
         <v>1</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" ht="49.5" customHeight="1">
-      <c r="B10" t="n" s="7">
+    <row r="10" ht="15" spans="1:14">
+      <c r="B10" s="7">
         <v>1004</v>
       </c>
-      <c r="C10" t="str" s="8">
-        <v>临时新手_鞋子</v>
-      </c>
-      <c r="D10" t="str" s="7">
-        <v>鞋子</v>
+      <c r="C10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" t="str" s="7">
-        <v>PVE移动力固定</v>
-      </c>
-      <c r="I10" t="str" s="7">
-        <v>1</v>
-      </c>
-      <c r="J10" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K10" t="n" s="7">
+      <c r="H10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="7">
         <v>1</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" ht="49.5" customHeight="1">
-      <c r="B11" t="n" s="7">
+    <row r="11" ht="15" spans="1:14">
+      <c r="B11" s="7">
         <v>2001</v>
       </c>
-      <c r="C11" t="str" s="8">
-        <v>临时守卫_头盔</v>
-      </c>
-      <c r="D11" t="str" s="7">
-        <v>头盔</v>
-      </c>
-      <c r="E11" t="str" s="7">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="F11" t="str" s="8">
-        <v>1星//2星//3星//4星</v>
-      </c>
-      <c r="G11" t="str" s="8">
-        <v>60//25//10//5</v>
-      </c>
-      <c r="H11" t="str" s="7">
-        <v>智力固定</v>
-      </c>
-      <c r="I11" t="str" s="7">
-        <v>8</v>
-      </c>
-      <c r="J11" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K11" t="n" s="7">
+      <c r="C11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="7">
         <v>1</v>
       </c>
-      <c r="L11" t="str" s="8">
-        <v>攻击固定//防御固定//智力固定//统帅固定</v>
-      </c>
-      <c r="M11" t="str" s="7">
-        <v>2//1//2//0.5</v>
-      </c>
-      <c r="N11" t="str" s="8">
-        <v>100//100//100//100</v>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="B12" t="n" s="7">
+      <c r="L11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:14">
+      <c r="B12" s="7">
         <v>2002</v>
       </c>
-      <c r="C12" t="str" s="8">
-        <v>临时守卫_衣服</v>
-      </c>
-      <c r="D12" t="str" s="7">
-        <v>衣服</v>
-      </c>
-      <c r="E12" t="str" s="7">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="F12" t="str" s="8">
-        <v>1星//2星//3星//4星</v>
-      </c>
-      <c r="G12" t="str" s="8">
-        <v>60//25//10//5</v>
-      </c>
-      <c r="H12" t="str" s="7">
-        <v>防御固定</v>
-      </c>
-      <c r="I12" t="str" s="7">
-        <v>6</v>
-      </c>
-      <c r="J12" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K12" t="n" s="7">
+      <c r="C12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="7">
         <v>1</v>
       </c>
-      <c r="L12" t="str" s="8">
-        <v>攻击固定//防御固定//智力固定//统帅固定</v>
-      </c>
-      <c r="M12" t="str" s="7">
-        <v>2//1//2//0.5</v>
-      </c>
-      <c r="N12" t="str" s="8">
-        <v>100//100//100//100</v>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1">
-      <c r="B13" t="n" s="7">
+      <c r="L12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:14">
+      <c r="B13" s="7">
         <v>2003</v>
       </c>
-      <c r="C13" t="str" s="8">
-        <v>临时守卫_武器</v>
-      </c>
-      <c r="D13" t="str" s="7">
-        <v>武器</v>
-      </c>
-      <c r="E13" t="str" s="7">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="F13" t="str" s="8">
-        <v>1星//2星//3星//4星</v>
-      </c>
-      <c r="G13" t="str" s="8">
-        <v>60//25//10//5</v>
-      </c>
-      <c r="H13" t="str" s="7">
-        <v>攻击固定</v>
-      </c>
-      <c r="I13" t="str" s="7">
-        <v>10</v>
-      </c>
-      <c r="J13" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K13" t="n" s="7">
+      <c r="C13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="7">
         <v>1</v>
       </c>
-      <c r="L13" t="str" s="8">
-        <v>攻击固定//防御固定//智力固定//统帅固定</v>
-      </c>
-      <c r="M13" t="str" s="7">
-        <v>2//1//2//0.5</v>
-      </c>
-      <c r="N13" t="str" s="8">
-        <v>100//100//100//100</v>
-      </c>
-    </row>
-    <row r="14" ht="49.5" customHeight="1">
-      <c r="B14" t="n" s="7">
+      <c r="L13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:14">
+      <c r="B14" s="7">
         <v>2004</v>
       </c>
-      <c r="C14" t="str" s="8">
-        <v>临时守卫_鞋子</v>
-      </c>
-      <c r="D14" t="str" s="7">
-        <v>鞋子</v>
-      </c>
-      <c r="E14" t="str" s="7">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="F14" t="str" s="8">
-        <v>1星//2星//3星//4星</v>
-      </c>
-      <c r="G14" t="str" s="8">
-        <v>60//25//10//5</v>
-      </c>
-      <c r="H14" t="str" s="7">
-        <v>先攻固定</v>
-      </c>
-      <c r="I14" t="str" s="7">
-        <v>2</v>
-      </c>
-      <c r="J14" t="str" s="7">
-        <v>100</v>
-      </c>
-      <c r="K14" t="n" s="7">
+      <c r="C14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="7">
         <v>1</v>
       </c>
-      <c r="L14" t="str" s="8">
-        <v>攻击固定//防御固定//智力固定//统帅固定</v>
-      </c>
-      <c r="M14" t="str" s="7">
-        <v>2//1//2//0.5</v>
-      </c>
-      <c r="N14" t="str" s="8">
-        <v>100//100//100//100</v>
+      <c r="L14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1969,211 +2056,210 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="5.625" customWidth="1"/>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="14.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="12" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.875" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:7">
+    <row r="1" ht="16.5" spans="1:7">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:7">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" ht="15" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:7">
       <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:7">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" ht="33.0" customHeight="1" spans="1:7">
+    <row r="7" ht="16.5" spans="1:7">
       <c r="A7" s="5"/>
       <c r="B7" s="5">
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <v>装备栏剪影-头盔</v>
-      </c>
-      <c r="F7" s="8" t="str">
-        <v>装备界面筛选-头盔</v>
+        <v>87</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="33.0" customHeight="1" spans="1:7">
+    <row r="8" ht="16.5" spans="1:7">
       <c r="A8" s="5"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <v>装备栏剪影-衣服</v>
-      </c>
-      <c r="F8" s="8" t="str">
-        <v>装备界面筛选-衣服</v>
+        <v>90</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="33.0" customHeight="1" spans="1:7">
+    <row r="9" ht="16.5" spans="1:7">
       <c r="A9" s="5"/>
       <c r="B9" s="5">
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <v>装备栏剪影-武器</v>
-      </c>
-      <c r="F9" s="8" t="str">
-        <v>装备界面筛选-武器</v>
+        <v>93</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="G9" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="33.0" customHeight="1" spans="1:7">
+    <row r="10" ht="16.5" spans="1:7">
       <c r="A10" s="5"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="8" t="str">
-        <v>装备栏剪影-鞋子</v>
-      </c>
-      <c r="F10" s="8" t="str">
-        <v>装备界面筛选-鞋子</v>
+        <v>96</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G10" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:7">
+    <row r="11" ht="16.5" spans="1:7">
       <c r="A11" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -2209,76 +2295,76 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:6">
       <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -2289,13 +2375,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -2307,13 +2393,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -2325,13 +2411,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D9" s="5">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -2343,13 +2429,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="D10" s="5">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="F10" s="5">
         <v>3</v>
@@ -2361,13 +2447,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="D11" s="5">
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="F11" s="5">
         <v>4</v>
